--- a/data/base/Backlog_15.xlsx
+++ b/data/base/Backlog_15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EACBEF8-E60B-48E0-9AD9-A31F2A8CA359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FA3E842-E5E8-4D4F-A7EC-B552E770E201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
+    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="32">
   <si>
     <t>Status</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>Eduardo Silva</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -239,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -264,10 +267,23 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -654,7 +670,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C2" s="6">
         <v>2026</v>
@@ -669,16 +685,16 @@
         <v>46136</v>
       </c>
       <c r="G2" s="6">
-        <v>13326</v>
-      </c>
-      <c r="H2" s="13">
-        <v>46104.708333333336</v>
+        <v>14991</v>
+      </c>
+      <c r="H2" s="12">
+        <v>46129.472511574073</v>
       </c>
       <c r="I2" s="7">
         <v>46132</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>13</v>
@@ -689,7 +705,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="6">
         <v>2026</v>
@@ -704,16 +720,16 @@
         <v>46136</v>
       </c>
       <c r="G3" s="6">
-        <v>14131</v>
-      </c>
-      <c r="H3" s="13">
-        <v>46122.642361111109</v>
+        <v>13326</v>
+      </c>
+      <c r="H3" s="12">
+        <v>46104.708333333336</v>
       </c>
       <c r="I3" s="7">
         <v>46132</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>13</v>
@@ -741,7 +757,7 @@
       <c r="G4" s="6">
         <v>14640</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <v>46126.624212962961</v>
       </c>
       <c r="I4" s="7">
@@ -776,7 +792,7 @@
       <c r="G5" s="6">
         <v>14845</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <v>46128.656087962961</v>
       </c>
       <c r="I5" s="7">
@@ -811,14 +827,14 @@
       <c r="G6" s="6">
         <v>14854</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <v>46128.675000000003</v>
       </c>
       <c r="I6" s="7">
         <v>46132</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>13</v>
@@ -846,14 +862,14 @@
       <c r="G7" s="6">
         <v>14905</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <v>46129.479803240742</v>
       </c>
       <c r="I7" s="7">
         <v>46132</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>13</v>
@@ -881,14 +897,14 @@
       <c r="G8" s="6">
         <v>14986</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <v>46132.427303240744</v>
       </c>
       <c r="I8" s="7">
         <v>46132</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>13</v>
@@ -899,7 +915,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="6">
         <v>2026</v>
@@ -914,16 +930,16 @@
         <v>46136</v>
       </c>
       <c r="G9" s="6">
-        <v>14991</v>
-      </c>
-      <c r="H9" s="13">
-        <v>46129.472511574073</v>
+        <v>15009</v>
+      </c>
+      <c r="H9" s="12">
+        <v>46132.606493055559</v>
       </c>
       <c r="I9" s="7">
         <v>46132</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>13</v>
@@ -934,7 +950,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C10" s="6">
         <v>2026</v>
@@ -949,16 +965,16 @@
         <v>46136</v>
       </c>
       <c r="G10" s="6">
-        <v>15009</v>
-      </c>
-      <c r="H10" s="13">
-        <v>46132.606493055559</v>
+        <v>14131</v>
+      </c>
+      <c r="H10" s="12">
+        <v>46122.642361111109</v>
       </c>
       <c r="I10" s="7">
         <v>46132</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>13</v>
@@ -986,14 +1002,14 @@
       <c r="G11" s="6">
         <v>15018</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <v>46132.631261574075</v>
       </c>
       <c r="I11" s="7">
         <v>46132</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>13</v>
@@ -1021,14 +1037,14 @@
       <c r="G12" s="6">
         <v>15062</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="12">
         <v>46133.409317129626</v>
       </c>
       <c r="I12" s="7">
         <v>46132</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>13</v>
@@ -1036,7 +1052,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{05C2F3D6-88A9-4A6C-8904-EE71E1E2FD4B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H9">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H12">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
@@ -1099,738 +1115,738 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="6" t="s">
+    <row r="2" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="13">
+        <v>15</v>
+      </c>
+      <c r="E2" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F2" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G2" s="14">
+        <v>15084</v>
+      </c>
+      <c r="H2" s="16">
+        <v>46118.492581018516</v>
+      </c>
+      <c r="I2" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="13">
+        <v>15</v>
+      </c>
+      <c r="E3" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F3" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G3" s="14">
+        <v>14409</v>
+      </c>
+      <c r="H3" s="16">
+        <v>46121.459606481483</v>
+      </c>
+      <c r="I3" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="13">
+        <v>15</v>
+      </c>
+      <c r="E4" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F4" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G4" s="14">
+        <v>14431</v>
+      </c>
+      <c r="H4" s="16">
+        <v>46121.522106481483</v>
+      </c>
+      <c r="I4" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="13">
+        <v>15</v>
+      </c>
+      <c r="E5" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F5" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G5" s="14">
+        <v>14891</v>
+      </c>
+      <c r="H5" s="16">
+        <v>46121.532824074071</v>
+      </c>
+      <c r="I5" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D6" s="13">
+        <v>15</v>
+      </c>
+      <c r="E6" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F6" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G6" s="14">
+        <v>14406</v>
+      </c>
+      <c r="H6" s="16">
+        <v>46121.583333333336</v>
+      </c>
+      <c r="I6" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="13">
+        <v>15</v>
+      </c>
+      <c r="E7" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F7" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G7" s="14">
+        <v>14682</v>
+      </c>
+      <c r="H7" s="16">
+        <v>46122.408472222225</v>
+      </c>
+      <c r="I7" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="13">
+        <v>15</v>
+      </c>
+      <c r="E8" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F8" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G8" s="14">
+        <v>14857</v>
+      </c>
+      <c r="H8" s="16">
+        <v>46122.69494212963</v>
+      </c>
+      <c r="I8" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="13">
+        <v>15</v>
+      </c>
+      <c r="E9" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F9" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G9" s="14">
+        <v>14925</v>
+      </c>
+      <c r="H9" s="16">
+        <v>46128.375625000001</v>
+      </c>
+      <c r="I9" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="13">
+        <v>15</v>
+      </c>
+      <c r="E10" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F10" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G10" s="14">
+        <v>14973</v>
+      </c>
+      <c r="H10" s="16">
+        <v>46127.351064814815</v>
+      </c>
+      <c r="I10" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="13">
+        <v>15</v>
+      </c>
+      <c r="E11" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F11" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G11" s="14">
+        <v>15050</v>
+      </c>
+      <c r="H11" s="16">
+        <v>46127.623252314814</v>
+      </c>
+      <c r="I11" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D12" s="13">
+        <v>15</v>
+      </c>
+      <c r="E12" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F12" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G12" s="14">
+        <v>15055</v>
+      </c>
+      <c r="H12" s="16">
+        <v>46127.631435185183</v>
+      </c>
+      <c r="I12" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="13">
+        <v>15</v>
+      </c>
+      <c r="E13" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F13" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G13" s="14">
+        <v>14790</v>
+      </c>
+      <c r="H13" s="16">
+        <v>46128.677094907405</v>
+      </c>
+      <c r="I13" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="13">
+        <v>15</v>
+      </c>
+      <c r="E14" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F14" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G14" s="14">
+        <v>14792</v>
+      </c>
+      <c r="H14" s="16">
+        <v>46128.697071759256</v>
+      </c>
+      <c r="I14" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="13">
+        <v>15</v>
+      </c>
+      <c r="E15" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F15" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G15" s="14">
+        <v>14900</v>
+      </c>
+      <c r="H15" s="16">
+        <v>46127.703645833331</v>
+      </c>
+      <c r="I15" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D16" s="13">
+        <v>15</v>
+      </c>
+      <c r="E16" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F16" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G16" s="14">
+        <v>14583</v>
+      </c>
+      <c r="H16" s="16">
+        <v>46128.624074074076</v>
+      </c>
+      <c r="I16" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="13">
+        <v>15</v>
+      </c>
+      <c r="E17" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F17" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G17" s="14">
+        <v>14972</v>
+      </c>
+      <c r="H17" s="16">
+        <v>46133.345231481479</v>
+      </c>
+      <c r="I17" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D18" s="13">
+        <v>15</v>
+      </c>
+      <c r="E18" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F18" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G18" s="14">
+        <v>15060</v>
+      </c>
+      <c r="H18" s="16">
+        <v>46129.437337962961</v>
+      </c>
+      <c r="I18" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D19" s="13">
+        <v>15</v>
+      </c>
+      <c r="E19" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F19" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G19" s="14">
+        <v>15138</v>
+      </c>
+      <c r="H19" s="16">
+        <v>46129.633750000001</v>
+      </c>
+      <c r="I19" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="1">
-        <v>15</v>
-      </c>
-      <c r="E2" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F2" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="C20" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D20" s="13">
+        <v>15</v>
+      </c>
+      <c r="E20" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F20" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G20" s="14">
         <v>14204</v>
       </c>
-      <c r="H2" s="13">
-        <v>46118.492581018516</v>
-      </c>
-      <c r="I2" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J2" s="6" t="s">
+      <c r="H20" s="16">
+        <v>46129.333587962959</v>
+      </c>
+      <c r="I20" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D21" s="13">
+        <v>15</v>
+      </c>
+      <c r="E21" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F21" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G21" s="14">
+        <v>14858</v>
+      </c>
+      <c r="H21" s="16">
+        <v>46127.66684027778</v>
+      </c>
+      <c r="I21" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J21" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="1">
-        <v>15</v>
-      </c>
-      <c r="E3" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F3" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G3" s="6">
-        <v>14372</v>
-      </c>
-      <c r="H3" s="13">
-        <v>46121.459606481483</v>
-      </c>
-      <c r="I3" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="1">
-        <v>15</v>
-      </c>
-      <c r="E4" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F4" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G4" s="6">
-        <v>14406</v>
-      </c>
-      <c r="H4" s="13">
-        <v>46121.522106481483</v>
-      </c>
-      <c r="I4" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="1">
-        <v>15</v>
-      </c>
-      <c r="E5" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F5" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G5" s="6">
-        <v>14409</v>
-      </c>
-      <c r="H5" s="13">
-        <v>46121.532824074071</v>
-      </c>
-      <c r="I5" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="1">
-        <v>15</v>
-      </c>
-      <c r="E6" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F6" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G6" s="6">
-        <v>14431</v>
-      </c>
-      <c r="H6" s="13">
-        <v>46121.583333333336</v>
-      </c>
-      <c r="I6" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="1">
-        <v>15</v>
-      </c>
-      <c r="E7" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F7" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G7" s="6">
-        <v>14449</v>
-      </c>
-      <c r="H7" s="13">
-        <v>46122.408472222225</v>
-      </c>
-      <c r="I7" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="1">
-        <v>15</v>
-      </c>
-      <c r="E8" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F8" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G8" s="6">
-        <v>14497</v>
-      </c>
-      <c r="H8" s="13">
-        <v>46122.69494212963</v>
-      </c>
-      <c r="I8" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="1">
-        <v>15</v>
-      </c>
-      <c r="E9" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F9" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G9" s="6">
-        <v>14583</v>
-      </c>
-      <c r="H9" s="13">
-        <v>46128.375625000001</v>
-      </c>
-      <c r="I9" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="1">
-        <v>15</v>
-      </c>
-      <c r="E10" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F10" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G10" s="6">
-        <v>14682</v>
-      </c>
-      <c r="H10" s="13">
-        <v>46127.351064814815</v>
-      </c>
-      <c r="I10" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="1">
-        <v>15</v>
-      </c>
-      <c r="E11" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F11" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G11" s="6">
-        <v>14790</v>
-      </c>
-      <c r="H11" s="13">
-        <v>46127.623252314814</v>
-      </c>
-      <c r="I11" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="1">
-        <v>15</v>
-      </c>
-      <c r="E12" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F12" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G12" s="6">
-        <v>14792</v>
-      </c>
-      <c r="H12" s="13">
-        <v>46127.631435185183</v>
-      </c>
-      <c r="I12" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D13" s="1">
-        <v>15</v>
-      </c>
-      <c r="E13" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F13" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G13" s="6">
-        <v>14799</v>
-      </c>
-      <c r="H13" s="13">
-        <v>46128.677094907405</v>
-      </c>
-      <c r="I13" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D14" s="1">
-        <v>15</v>
-      </c>
-      <c r="E14" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F14" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G14" s="6">
-        <v>14857</v>
-      </c>
-      <c r="H14" s="13">
-        <v>46128.697071759256</v>
-      </c>
-      <c r="I14" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="K21" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D15" s="1">
-        <v>15</v>
-      </c>
-      <c r="E15" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F15" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G15" s="6">
-        <v>14858</v>
-      </c>
-      <c r="H15" s="13">
-        <v>46127.703645833331</v>
-      </c>
-      <c r="I15" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D16" s="1">
-        <v>15</v>
-      </c>
-      <c r="E16" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F16" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G16" s="6">
-        <v>14891</v>
-      </c>
-      <c r="H16" s="13">
-        <v>46128.624074074076</v>
-      </c>
-      <c r="I16" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D17" s="1">
-        <v>15</v>
-      </c>
-      <c r="E17" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F17" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G17" s="6">
-        <v>14898</v>
-      </c>
-      <c r="H17" s="13">
-        <v>46133.345231481479</v>
-      </c>
-      <c r="I17" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D18" s="1">
-        <v>15</v>
-      </c>
-      <c r="E18" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F18" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G18" s="6">
-        <v>14900</v>
-      </c>
-      <c r="H18" s="13">
-        <v>46129.437337962961</v>
-      </c>
-      <c r="I18" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="12" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D19" s="1">
-        <v>15</v>
-      </c>
-      <c r="E19" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F19" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G19" s="6">
-        <v>14925</v>
-      </c>
-      <c r="H19" s="13">
-        <v>46129.633750000001</v>
-      </c>
-      <c r="I19" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D20" s="1">
-        <v>15</v>
-      </c>
-      <c r="E20" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F20" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="C22" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D22" s="13">
+        <v>15</v>
+      </c>
+      <c r="E22" s="15">
+        <v>46132</v>
+      </c>
+      <c r="F22" s="15">
+        <v>46136</v>
+      </c>
+      <c r="G22" s="14">
         <v>14940</v>
       </c>
-      <c r="H20" s="13">
-        <v>46129.333587962959</v>
-      </c>
-      <c r="I20" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D21" s="1">
-        <v>15</v>
-      </c>
-      <c r="E21" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F21" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G21" s="6">
-        <v>14961</v>
-      </c>
-      <c r="H21" s="13">
-        <v>46127.66684027778</v>
-      </c>
-      <c r="I21" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D22" s="1">
-        <v>15</v>
-      </c>
-      <c r="E22" s="7">
-        <v>46132</v>
-      </c>
-      <c r="F22" s="7">
-        <v>46136</v>
-      </c>
-      <c r="G22" s="6">
-        <v>14972</v>
-      </c>
-      <c r="H22" s="13">
+      <c r="H22" s="16">
         <v>46132.377337962964</v>
       </c>
-      <c r="I22" s="7">
-        <v>46132</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K22" s="1" t="s">
+      <c r="I22" s="15">
+        <v>46132</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1839,7 +1855,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C23" s="1">
         <v>2026</v>
@@ -1854,9 +1870,9 @@
         <v>46136</v>
       </c>
       <c r="G23" s="6">
-        <v>14973</v>
-      </c>
-      <c r="H23" s="13">
+        <v>14449</v>
+      </c>
+      <c r="H23" s="12">
         <v>46132.380370370367</v>
       </c>
       <c r="I23" s="7">
@@ -1889,9 +1905,9 @@
         <v>46136</v>
       </c>
       <c r="G24" s="6">
-        <v>15014</v>
-      </c>
-      <c r="H24" s="13">
+        <v>14799</v>
+      </c>
+      <c r="H24" s="12">
         <v>46133.401053240741</v>
       </c>
       <c r="I24" s="7">
@@ -1924,16 +1940,16 @@
         <v>46136</v>
       </c>
       <c r="G25" s="6">
-        <v>15019</v>
-      </c>
-      <c r="H25" s="13">
+        <v>14898</v>
+      </c>
+      <c r="H25" s="12">
         <v>46132.648634259262</v>
       </c>
       <c r="I25" s="7">
         <v>46132</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>1</v>
@@ -1944,7 +1960,7 @@
         <v>16</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C26" s="1">
         <v>2026</v>
@@ -1959,9 +1975,9 @@
         <v>46136</v>
       </c>
       <c r="G26" s="6">
-        <v>15050</v>
-      </c>
-      <c r="H26" s="13">
+        <v>15014</v>
+      </c>
+      <c r="H26" s="12">
         <v>46133.360081018516</v>
       </c>
       <c r="I26" s="7">
@@ -1979,7 +1995,7 @@
         <v>16</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C27" s="1">
         <v>2026</v>
@@ -1994,16 +2010,16 @@
         <v>46136</v>
       </c>
       <c r="G27" s="6">
-        <v>15055</v>
-      </c>
-      <c r="H27" s="13">
+        <v>15019</v>
+      </c>
+      <c r="H27" s="12">
         <v>46133.383645833332</v>
       </c>
       <c r="I27" s="7">
         <v>46132</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>1</v>
@@ -2014,7 +2030,7 @@
         <v>16</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C28" s="1">
         <v>2026</v>
@@ -2029,9 +2045,9 @@
         <v>46136</v>
       </c>
       <c r="G28" s="6">
-        <v>15060</v>
-      </c>
-      <c r="H28" s="13">
+        <v>15152</v>
+      </c>
+      <c r="H28" s="12">
         <v>46133.400509259256</v>
       </c>
       <c r="I28" s="7">
@@ -2049,7 +2065,7 @@
         <v>16</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C29" s="1">
         <v>2026</v>
@@ -2064,16 +2080,16 @@
         <v>46136</v>
       </c>
       <c r="G29" s="6">
-        <v>15084</v>
-      </c>
-      <c r="H29" s="13">
+        <v>15240</v>
+      </c>
+      <c r="H29" s="12">
         <v>46132.544768518521</v>
       </c>
       <c r="I29" s="7">
         <v>46132</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>1</v>
@@ -2084,7 +2100,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1">
         <v>2026</v>
@@ -2099,9 +2115,9 @@
         <v>46136</v>
       </c>
       <c r="G30" s="6">
-        <v>15103</v>
-      </c>
-      <c r="H30" s="13">
+        <v>14372</v>
+      </c>
+      <c r="H30" s="12">
         <v>46132.643611111111</v>
       </c>
       <c r="I30" s="7">
@@ -2119,7 +2135,7 @@
         <v>16</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C31" s="1">
         <v>2026</v>
@@ -2134,16 +2150,16 @@
         <v>46136</v>
       </c>
       <c r="G31" s="6">
-        <v>15138</v>
-      </c>
-      <c r="H31" s="13">
+        <v>15103</v>
+      </c>
+      <c r="H31" s="12">
         <v>46133.366655092592</v>
       </c>
       <c r="I31" s="7">
         <v>46132</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>1</v>
@@ -2154,7 +2170,7 @@
         <v>16</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C32" s="1">
         <v>2026</v>
@@ -2169,9 +2185,9 @@
         <v>46136</v>
       </c>
       <c r="G32" s="6">
-        <v>15152</v>
-      </c>
-      <c r="H32" s="13">
+        <v>14497</v>
+      </c>
+      <c r="H32" s="12">
         <v>46133.442928240744</v>
       </c>
       <c r="I32" s="7">
@@ -2189,7 +2205,7 @@
         <v>16</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C33" s="1">
         <v>2026</v>
@@ -2204,9 +2220,9 @@
         <v>46136</v>
       </c>
       <c r="G33" s="6">
-        <v>15240</v>
-      </c>
-      <c r="H33" s="13">
+        <v>14961</v>
+      </c>
+      <c r="H33" s="12">
         <v>46133.416666666664</v>
       </c>
       <c r="I33" s="7">
@@ -2221,7 +2237,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G23">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G33">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
